--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:39:19+00:00</t>
+    <t>2024-03-20T14:46:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,9 +986,6 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation. Correspond à la notion de Fonction dans le NOS.</t>
-  </si>
-  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
@@ -1001,7 +998,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation</t>
+    <t>Specific specialty associated with the organization | spécialité ordinale du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
     <t>Specific specialty of the practitioner.</t>
@@ -1589,7 +1586,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.15625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -5449,13 +5446,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y34" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y34" s="2"/>
+      <c r="Z34" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5488,10 +5483,10 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>294</v>
@@ -5502,10 +5497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5531,13 +5526,13 @@
         <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5563,11 +5558,11 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5585,7 +5580,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5600,13 +5595,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5614,10 +5609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5640,13 +5635,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>300</v>
@@ -5699,7 +5694,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5717,21 +5712,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5754,13 +5749,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>300</v>
@@ -5813,7 +5808,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5828,10 +5823,10 @@
         <v>274</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5842,10 +5837,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5868,17 +5863,17 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5927,7 +5922,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5939,16 +5934,16 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AK38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5956,10 +5951,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5982,16 +5977,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6041,7 +6036,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6059,7 +6054,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6070,10 +6065,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6182,10 +6177,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6296,14 +6291,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6325,10 +6320,10 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>114</v>
@@ -6383,7 +6378,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6412,10 +6407,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6441,13 +6436,13 @@
         <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6476,11 +6471,11 @@
         <v>224</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6497,7 +6492,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6515,7 +6510,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6526,10 +6521,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6555,10 +6550,10 @@
         <v>279</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6609,7 +6604,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6627,7 +6622,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6638,10 +6633,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6664,16 +6659,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6723,7 +6718,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6741,7 +6736,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6752,10 +6747,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6778,16 +6773,16 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="N46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6837,7 +6832,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6855,7 +6850,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6866,10 +6861,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6892,13 +6887,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6949,7 +6944,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6967,7 +6962,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6978,10 +6973,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7090,10 +7085,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7204,14 +7199,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7233,10 +7228,10 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>114</v>
@@ -7291,7 +7286,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7320,10 +7315,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7349,13 +7344,13 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7405,7 +7400,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7434,10 +7429,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7463,10 +7458,10 @@
         <v>259</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>262</v>
@@ -7519,7 +7514,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7534,10 +7529,10 @@
         <v>264</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7548,10 +7543,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7577,13 +7572,13 @@
         <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7633,7 +7628,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7651,7 +7646,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7662,10 +7657,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7688,19 +7683,19 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>300</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7749,7 +7744,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7767,7 +7762,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:46:52+00:00</t>
+    <t>2024-03-20T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -974,10 +974,10 @@
     <t>PractitionerRole.code</t>
   </si>
   <si>
-    <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation</t>
-  </si>
-  <si>
-    <t>The role a person plays representing an organization | Situation d'exercice (Fonction dans le NOS)</t>
+    <t>The role a person plays representing an organization | Rôle ou fonction du professionnel de santé au sein de l'organisation</t>
+  </si>
+  <si>
+    <t>Roles which this practitioner is authorized to perform for the organization.</t>
   </si>
   <si>
     <t>A person may have more than one role.</t>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T15:41:15+00:00</t>
+    <t>2024-03-20T17:15:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T17:15:33+00:00</t>
+    <t>2024-03-25T10:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
